--- a/RoomImport/Пример импорта.xlsx
+++ b/RoomImport/Пример импорта.xlsx
@@ -5,6 +5,8 @@
   <sheets>
     <sheet name="Квартиры" r:id="rId1" sheetId="1" state="visible"/>
     <sheet name="Машиноместа" r:id="rId2" sheetId="2" state="visible"/>
+    <sheet name="Коммерческое помещение" r:id="rId3" sheetId="3" state="visible"/>
+    <sheet name="Кладовая" r:id="rId4" sheetId="4" state="visible"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -103,7 +105,37 @@
     <t>№ маш 1 -1-2</t>
   </si>
   <si>
+    <t>лит. 1.2</t>
+  </si>
+  <si>
     <t>№ маш 1 -1-3</t>
+  </si>
+  <si>
+    <t>Коммерческое помещение</t>
+  </si>
+  <si>
+    <t>№ к/п 1 -1-1</t>
+  </si>
+  <si>
+    <t>№ к/п 1 -1-2</t>
+  </si>
+  <si>
+    <t>3/3</t>
+  </si>
+  <si>
+    <t>№ к/п 1 -1-3</t>
+  </si>
+  <si>
+    <t>Кладовая</t>
+  </si>
+  <si>
+    <t>№ клад 1 -1-1</t>
+  </si>
+  <si>
+    <t>№ клад 1 -1-2</t>
+  </si>
+  <si>
+    <t>№ клад 1 -1-3</t>
   </si>
 </sst>
 </file>
@@ -113,6 +145,7 @@
   <numFmts>
     <numFmt co:extendedFormatCode="General" formatCode="General" numFmtId="1000"/>
     <numFmt co:extendedFormatCode="0" formatCode="0" numFmtId="1001"/>
+    <numFmt co:extendedFormatCode="@" formatCode="@" numFmtId="1002"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -225,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf applyFont="true" applyNumberFormat="true" borderId="0" fillId="0" fontId="1" numFmtId="1000" quotePrefix="false"/>
     <xf applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true" applyNumberFormat="true" borderId="1" fillId="2" fontId="2" numFmtId="1001" quotePrefix="false">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -252,6 +285,9 @@
       <alignment wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="true" applyFont="true" borderId="5" fillId="0" fontId="0" quotePrefix="false">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFont="true" applyNumberFormat="true" borderId="5" fillId="0" fontId="0" numFmtId="1002" quotePrefix="false">
       <alignment wrapText="true"/>
     </xf>
   </cellXfs>
@@ -838,14 +874,14 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="9.14062530925693" defaultRowHeight="14.3999996185303" zeroHeight="false"/>
   <cols>
     <col customWidth="true" max="1" min="1" outlineLevel="0" width="2.66406252246738"/>
     <col customWidth="true" max="6" min="2" outlineLevel="0" width="12.554687112768"/>
     <col bestFit="true" customWidth="true" max="7" min="7" outlineLevel="0" width="15.6806061291953"/>
-    <col customWidth="true" max="16" min="8" outlineLevel="0" width="12.554687112768"/>
-    <col customWidth="true" max="20" min="17" outlineLevel="0" width="34.7773433026347"/>
+    <col customWidth="true" max="15" min="8" outlineLevel="0" width="12.554687112768"/>
+    <col customWidth="true" max="19" min="16" outlineLevel="0" width="34.7773433026347"/>
   </cols>
   <sheetData>
     <row ht="15" outlineLevel="0" r="1"/>
@@ -878,24 +914,21 @@
         <v>8</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="L2" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="M2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -928,24 +961,21 @@
         <v>2</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>10</v>
+        <v>800000</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>800000</v>
+        <v>2</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>2</v>
+        <v>800003</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>800003</v>
-      </c>
-      <c r="P3" s="8" t="n">
         <v>800006</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>28</v>
       </c>
     </row>
@@ -978,24 +1008,21 @@
         <v>2</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>2</v>
+        <v>11.2</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>11.2</v>
+        <v>800001</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>800001</v>
+        <v>2</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>2</v>
+        <v>800004</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>800004</v>
-      </c>
-      <c r="P4" s="8" t="n">
         <v>800007</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1019,7 +1046,7 @@
         <v>27</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>-1</v>
@@ -1028,29 +1055,442 @@
         <v>2</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="L5" s="8" t="n">
         <v>800002</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="M5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="N5" s="8" t="n">
         <v>800005</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="O5" s="9" t="n">
         <v>800008</v>
       </c>
-      <c r="Q5" s="9" t="s">
-        <v>30</v>
+      <c r="P5" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.300000011920929" header="0.300000011920929" left="0.700000047683716" right="0.700000047683716" top="0.75"/>
   <pageSetup fitToHeight="0" fitToWidth="0" orientation="portrait" paperHeight="297mm" paperSize="9" paperWidth="210mm" scale="100"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="9.14062530925693" defaultRowHeight="14.3999996185303" zeroHeight="false"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" outlineLevel="0" width="2.66406252246738"/>
+    <col customWidth="true" max="6" min="2" outlineLevel="0" width="12.554687112768"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" outlineLevel="0" width="15.6806061291953"/>
+    <col customWidth="true" max="15" min="8" outlineLevel="0" width="12.554687112768"/>
+    <col customWidth="true" max="19" min="16" outlineLevel="0" width="34.7773433026347"/>
+  </cols>
+  <sheetData>
+    <row ht="15" outlineLevel="0" r="1"/>
+    <row ht="93" outlineLevel="0" r="2">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3">
+      <c r="B3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>800000</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>800003</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>800006</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4">
+      <c r="B4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>800004</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>800007</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5">
+      <c r="B5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>800002</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>800005</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>800008</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
+  <sheetPr>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
+  </sheetPr>
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="9.14062530925693" defaultRowHeight="14.3999996185303" zeroHeight="false"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" outlineLevel="0" width="2.66406252246738"/>
+    <col customWidth="true" max="6" min="2" outlineLevel="0" width="12.554687112768"/>
+    <col bestFit="true" customWidth="true" max="7" min="7" outlineLevel="0" width="15.6806061291953"/>
+    <col customWidth="true" max="15" min="8" outlineLevel="0" width="12.554687112768"/>
+    <col customWidth="true" max="19" min="16" outlineLevel="0" width="34.7773433026347"/>
+  </cols>
+  <sheetData>
+    <row ht="15" outlineLevel="0" r="1"/>
+    <row ht="93" outlineLevel="0" r="2">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3">
+      <c r="B3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>800000</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>800003</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>800006</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4">
+      <c r="B4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>800001</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>800004</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>800007</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5">
+      <c r="B5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>800002</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>800005</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>800008</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/RoomImport/Пример импорта.xlsx
+++ b/RoomImport/Пример импорта.xlsx
@@ -94,6 +94,24 @@
   </si>
   <si>
     <t>№ првк 1 -1-6</t>
+  </si>
+  <si>
+    <t>№ првк 1 -2-1</t>
+  </si>
+  <si>
+    <t>№ првк 1 -2-2</t>
+  </si>
+  <si>
+    <t>№ првк 1 -2-3</t>
+  </si>
+  <si>
+    <t>№ првк 1 -2-4</t>
+  </si>
+  <si>
+    <t>№ првк 1 -2-5</t>
+  </si>
+  <si>
+    <t>№ првк 1 -2-6</t>
   </si>
   <si>
     <t>Машиноместо</t>
@@ -504,7 +522,7 @@
   <sheetPr>
     <outlinePr summaryBelow="true" summaryRight="true"/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="9.14062530925693" defaultRowHeight="14.3999996185303" zeroHeight="false"/>
   <cols>
     <col customWidth="true" max="1" min="1" outlineLevel="0" width="2.66406252246738"/>
@@ -862,6 +880,330 @@
       <c r="Q8" s="8" t="s">
         <v>26</v>
       </c>
+    </row>
+    <row outlineLevel="0" r="9">
+      <c r="A9" s="0" t="n"/>
+      <c r="B9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>1000002</v>
+      </c>
+      <c r="Q9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="0" t="n"/>
+      <c r="S9" s="0" t="n"/>
+      <c r="T9" s="0" t="n"/>
+    </row>
+    <row outlineLevel="0" r="10">
+      <c r="A10" s="0" t="n"/>
+      <c r="B10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>1000003</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>1000004</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>1000005</v>
+      </c>
+      <c r="Q10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" s="0" t="n"/>
+      <c r="S10" s="0" t="n"/>
+      <c r="T10" s="0" t="n"/>
+    </row>
+    <row outlineLevel="0" r="11">
+      <c r="A11" s="0" t="n"/>
+      <c r="B11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>1000006</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>1000007</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>1000008</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" s="0" t="n"/>
+      <c r="S11" s="0" t="n"/>
+      <c r="T11" s="0" t="n"/>
+    </row>
+    <row outlineLevel="0" r="12">
+      <c r="A12" s="0" t="n"/>
+      <c r="B12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>1000009</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" s="0" t="n"/>
+      <c r="S12" s="0" t="n"/>
+      <c r="T12" s="0" t="n"/>
+    </row>
+    <row outlineLevel="0" r="13">
+      <c r="A13" s="0" t="n"/>
+      <c r="B13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>1000012</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>1000013</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>1000014</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="R13" s="0" t="n"/>
+      <c r="S13" s="0" t="n"/>
+      <c r="T13" s="0" t="n"/>
+    </row>
+    <row outlineLevel="0" r="14">
+      <c r="A14" s="0" t="n"/>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>71.02</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>1000015</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>1000016</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>1000017</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="0" t="n"/>
+      <c r="S14" s="0" t="n"/>
+      <c r="T14" s="0" t="n"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.300000011920929" header="0.300000011920929" left="0.25" right="0.25" top="0.75"/>
@@ -949,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>20</v>
@@ -976,7 +1318,7 @@
         <v>800006</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -996,7 +1338,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>20</v>
@@ -1023,7 +1365,7 @@
         <v>800007</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -1043,10 +1385,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>-1</v>
@@ -1070,7 +1412,7 @@
         <v>800008</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1159,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>20</v>
@@ -1186,7 +1528,7 @@
         <v>800006</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -1206,7 +1548,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>20</v>
@@ -1233,7 +1575,7 @@
         <v>800007</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -1250,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>2</v>
@@ -1280,7 +1622,7 @@
         <v>800008</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1367,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>20</v>
@@ -1394,7 +1736,7 @@
         <v>800006</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
@@ -1414,7 +1756,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>20</v>
@@ -1441,7 +1783,7 @@
         <v>800007</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
@@ -1461,10 +1803,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>-1</v>
@@ -1488,7 +1830,7 @@
         <v>800008</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
